--- a/output/yearly_surface_area_iteration_84_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_84_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497650415163</v>
+        <v>10.84497623298814</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907254101854</v>
+        <v>37.78907159615558</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.762458113301277</v>
+        <v>4.858669388317464</v>
       </c>
       <c r="C2" t="n">
-        <v>7.065638227464294</v>
+        <v>10.24748253692821</v>
       </c>
       <c r="D2" t="n">
-        <v>18.60019200466007</v>
+        <v>27.98766355266807</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.84188186635403</v>
+        <v>17.09222753093697</v>
       </c>
       <c r="C3" t="n">
-        <v>19.06554041647306</v>
+        <v>21.95678740547991</v>
       </c>
       <c r="D3" t="n">
-        <v>77.56788611254049</v>
+        <v>88.42601572151021</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.40378571054848</v>
+        <v>33.06820792214531</v>
       </c>
       <c r="C4" t="n">
-        <v>48.43452298901639</v>
+        <v>66.71073825127502</v>
       </c>
       <c r="D4" t="n">
-        <v>113.4861076201143</v>
+        <v>103.8502539029318</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.28311285838414</v>
+        <v>40.64435495581795</v>
       </c>
       <c r="C5" t="n">
-        <v>84.8475453395306</v>
+        <v>99.57376090323277</v>
       </c>
       <c r="D5" t="n">
-        <v>80.84692344472485</v>
+        <v>69.97406762019142</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.42524529132167</v>
+        <v>37.79630486579796</v>
       </c>
       <c r="C6" t="n">
-        <v>100.5486363735499</v>
+        <v>105.0970734873253</v>
       </c>
       <c r="D6" t="n">
-        <v>51.52211951887262</v>
+        <v>46.36990756698535</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.60205768907732</v>
+        <v>25.99078872223005</v>
       </c>
       <c r="C7" t="n">
-        <v>88.45252290952486</v>
+        <v>105.5202067478557</v>
       </c>
       <c r="D7" t="n">
-        <v>39.94436884268997</v>
+        <v>38.92629647338602</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.93867397844697</v>
+        <v>13.51866588747858</v>
       </c>
       <c r="C8" t="n">
-        <v>59.74916528046088</v>
+        <v>79.77681844709581</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>45.81718360949438</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
         <v>34.59188035913637</v>
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>23.35381438862312</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.692044149025871</v>
+        <v>7.685047384423157</v>
       </c>
       <c r="C21" t="n">
-        <v>94.22754082556692</v>
+        <v>94.14183045918368</v>
       </c>
       <c r="D21" t="n">
-        <v>7.692044149025871</v>
+        <v>8.645678307476052</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.940375431948202</v>
+        <v>6.865361695797945</v>
       </c>
       <c r="C2" t="n">
-        <v>5.634250074672444</v>
+        <v>5.704935909378215</v>
       </c>
       <c r="D2" t="n">
-        <v>20.11404696460865</v>
+        <v>24.43177336788612</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.36573422979433</v>
+        <v>16.6062624173348</v>
       </c>
       <c r="C3" t="n">
-        <v>23.38032157663779</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D3" t="n">
-        <v>74.45083715155687</v>
+        <v>89.48630324209677</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.83397113145782</v>
+        <v>32.80019079888594</v>
       </c>
       <c r="C4" t="n">
-        <v>47.51560713784138</v>
+        <v>60.69949705817179</v>
       </c>
       <c r="D4" t="n">
-        <v>123.3389275799353</v>
+        <v>121.2586041946363</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.866491978885</v>
+        <v>44.57134577280519</v>
       </c>
       <c r="C5" t="n">
-        <v>87.05647767408593</v>
+        <v>109.7593933347934</v>
       </c>
       <c r="D5" t="n">
-        <v>100.8009455335413</v>
+        <v>87.0810213666921</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.32086123950202</v>
+        <v>45.64537776125121</v>
       </c>
       <c r="C6" t="n">
-        <v>116.3272854762046</v>
+        <v>130.294610064524</v>
       </c>
       <c r="D6" t="n">
-        <v>62.75233150775189</v>
+        <v>56.23156325614456</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.54323494228053</v>
+        <v>35.09355343600648</v>
       </c>
       <c r="C7" t="n">
-        <v>116.5393429803219</v>
+        <v>126.8398398932794</v>
       </c>
       <c r="D7" t="n">
-        <v>45.27427712904591</v>
+        <v>42.51949307092936</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.94973524510094</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="C8" t="n">
-        <v>87.12029127486194</v>
+        <v>108.7334669838555</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.6484365108884</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>55.35780779936488</v>
+        <v>70.11249404649018</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>37.15424186722054</v>
+        <v>42.56367171762047</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.877725782656209</v>
+        <v>7.865483266311561</v>
       </c>
       <c r="C21" t="n">
-        <v>103.3951508973628</v>
+        <v>102.2512824620503</v>
       </c>
       <c r="D21" t="n">
-        <v>8.862441505488235</v>
+        <v>9.83185408288945</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.035604959260143</v>
+        <v>8.08272884906399</v>
       </c>
       <c r="C2" t="n">
-        <v>7.765624340592271</v>
+        <v>13.08669689760998</v>
       </c>
       <c r="D2" t="n">
-        <v>26.86748942212246</v>
+        <v>22.56939797292992</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.89159114637213</v>
+        <v>19.20298509506761</v>
       </c>
       <c r="C3" t="n">
-        <v>22.48693116577319</v>
+        <v>26.58081909248239</v>
       </c>
       <c r="D3" t="n">
-        <v>72.90949325588937</v>
+        <v>87.79769719079225</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.00890214926301</v>
+        <v>31.57496966398591</v>
       </c>
       <c r="C4" t="n">
-        <v>52.05913551309561</v>
+        <v>68.25502739005525</v>
       </c>
       <c r="D4" t="n">
-        <v>129.1842534110208</v>
+        <v>134.6722230777605</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.50462798664542</v>
+        <v>46.24031687002478</v>
       </c>
       <c r="C5" t="n">
-        <v>87.13010875190443</v>
+        <v>109.3666942530947</v>
       </c>
       <c r="D5" t="n">
-        <v>118.6687537508332</v>
+        <v>104.6297615801038</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.72087452348698</v>
+        <v>52.1258943569844</v>
       </c>
       <c r="C6" t="n">
-        <v>125.2631530802591</v>
+        <v>148.3273518961294</v>
       </c>
       <c r="D6" t="n">
-        <v>76.07562960208534</v>
+        <v>67.94479511551327</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.06520592577034</v>
+        <v>43.05847256056086</v>
       </c>
       <c r="C7" t="n">
-        <v>139.1165949348858</v>
+        <v>154.3277938644858</v>
       </c>
       <c r="D7" t="n">
-        <v>51.86180422454201</v>
+        <v>47.31042186765379</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.54493639578176</v>
+        <v>27.53802310412303</v>
       </c>
       <c r="C8" t="n">
-        <v>117.9962565734241</v>
+        <v>134.268724771315</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>40.63944621729671</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.9734360587231</v>
+        <v>14.31093628480575</v>
       </c>
       <c r="C9" t="n">
-        <v>78.4328058399819</v>
+        <v>97.84686669146257</v>
       </c>
       <c r="D9" t="n">
-        <v>37.60780930658255</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>60.07314202286233</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>39.626282586514</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>36.45032876327558</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.049487849735435</v>
+        <v>8.031066363841866</v>
       </c>
       <c r="C21" t="n">
-        <v>111.6866439150792</v>
+        <v>110.4271625028257</v>
       </c>
       <c r="D21" t="n">
-        <v>10.06185981216929</v>
+        <v>11.04271625028256</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.292421947145307</v>
+        <v>7.291440199441061</v>
       </c>
       <c r="C2" t="n">
-        <v>5.156138942704248</v>
+        <v>8.898561191293089</v>
       </c>
       <c r="D2" t="n">
-        <v>21.8389776809703</v>
+        <v>18.72978270162065</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.01354884587698</v>
+        <v>22.61455836732528</v>
       </c>
       <c r="C3" t="n">
-        <v>34.74895999181586</v>
+        <v>43.9528447191297</v>
       </c>
       <c r="D3" t="n">
-        <v>83.05094704075893</v>
+        <v>96.82486733134168</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.7769476491535</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="C4" t="n">
-        <v>72.97723384748241</v>
+        <v>92.59353472603793</v>
       </c>
       <c r="D4" t="n">
-        <v>127.6272015520854</v>
+        <v>125.5085900063207</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.5203927031756</v>
+        <v>29.35425635697964</v>
       </c>
       <c r="C5" t="n">
-        <v>74.83371875621313</v>
+        <v>88.62727400088082</v>
       </c>
       <c r="D5" t="n">
-        <v>78.4907289545325</v>
+        <v>68.72233929727673</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.07427833482005</v>
+        <v>26.72709950041517</v>
       </c>
       <c r="C6" t="n">
-        <v>91.61276876949537</v>
+        <v>101.6354310821511</v>
       </c>
       <c r="D6" t="n">
-        <v>34.13340418125311</v>
+        <v>31.15478164656829</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>18.20552942755285</v>
       </c>
       <c r="C7" t="n">
-        <v>82.94295479329178</v>
+        <v>94.38129729547136</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>28.56591295046944</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>57.74639996379738</v>
+        <v>72.09955139988574</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>45.81718360949438</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.461061568097507</v>
+        <v>4.354051068334604</v>
       </c>
       <c r="C2" t="n">
-        <v>2.783254741539707</v>
+        <v>4.433572632378596</v>
       </c>
       <c r="D2" t="n">
-        <v>14.97361598517235</v>
+        <v>13.29580915861455</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.34381698513141</v>
+        <v>24.38170423496954</v>
       </c>
       <c r="C3" t="n">
-        <v>27.60674544342031</v>
+        <v>40.02585390214246</v>
       </c>
       <c r="D3" t="n">
-        <v>82.69260912870885</v>
+        <v>90.81166264282996</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.14027641518283</v>
+        <v>31.21761349964007</v>
       </c>
       <c r="C4" t="n">
-        <v>82.58756212435443</v>
+        <v>104.411813589761</v>
       </c>
       <c r="D4" t="n">
-        <v>139.7517856995335</v>
+        <v>143.4912627050096</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.66198535676539</v>
+        <v>32.42221793275092</v>
       </c>
       <c r="C5" t="n">
-        <v>104.5315868096792</v>
+        <v>127.9462695559656</v>
       </c>
       <c r="D5" t="n">
-        <v>98.44475104334893</v>
+        <v>89.48630324209678</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.43403996293088</v>
+        <v>32.16107304342126</v>
       </c>
       <c r="C6" t="n">
-        <v>107.3109145604019</v>
+        <v>121.9222656427072</v>
       </c>
       <c r="D6" t="n">
-        <v>43.79380159104173</v>
+        <v>39.48687441251096</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.48122060599696</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C7" t="n">
-        <v>105.3405469179785</v>
+        <v>118.2161680591754</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>75.77128781376882</v>
+        <v>92.04375601165971</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>44.70780870369548</v>
+        <v>52.14062057254808</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
+        <v>29.49759152179966</v>
+      </c>
+      <c r="D11" t="n">
         <v>29.67528785626833</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.242933651305467</v>
+        <v>4.950953672516665</v>
       </c>
       <c r="C2" t="n">
-        <v>8.572620953483149</v>
+        <v>10.27595322035137</v>
       </c>
       <c r="D2" t="n">
-        <v>16.42562083975338</v>
+        <v>14.24319569321272</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.15528036818702</v>
+        <v>19.53677931451153</v>
       </c>
       <c r="C3" t="n">
-        <v>18.4666743168825</v>
+        <v>28.04853191033137</v>
       </c>
       <c r="D3" t="n">
-        <v>75.87437132271474</v>
+        <v>81.92684591939633</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.58094226566941</v>
+        <v>38.90077103307561</v>
       </c>
       <c r="C4" t="n">
-        <v>75.3638625165064</v>
+        <v>102.0634730812026</v>
       </c>
       <c r="D4" t="n">
-        <v>148.4942490058513</v>
+        <v>154.2374730756951</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.12326790904115</v>
+        <v>39.09810232162923</v>
       </c>
       <c r="C5" t="n">
-        <v>129.9343086570654</v>
+        <v>159.5340019401067</v>
       </c>
       <c r="D5" t="n">
-        <v>123.2338805755809</v>
+        <v>115.4044426342126</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.78751019418875</v>
+        <v>37.59504658642736</v>
       </c>
       <c r="C6" t="n">
-        <v>135.7688352634042</v>
+        <v>161.5701466787146</v>
       </c>
       <c r="D6" t="n">
-        <v>61.26302024040947</v>
+        <v>54.37998708593508</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.72183090899544</v>
+        <v>25.81112889235289</v>
       </c>
       <c r="C7" t="n">
-        <v>130.7923561505771</v>
+        <v>146.5425345698086</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>34.55457394637499</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C8" t="n">
-        <v>106.3969074477481</v>
+        <v>122.0852357616121</v>
       </c>
       <c r="D8" t="n">
-        <v>30.54217107911827</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>67.00624431025328</v>
+        <v>78.76561831172157</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>41.70955121492574</v>
+        <v>45.55309347705201</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2509,7 +2509,7 @@
         <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.590251354430586</v>
+        <v>2.911863690796039</v>
       </c>
       <c r="C2" t="n">
-        <v>3.875939936366407</v>
+        <v>4.790928796724435</v>
       </c>
       <c r="D2" t="n">
-        <v>11.36372967665683</v>
+        <v>9.969647936626359</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.33476027161494</v>
+        <v>20.05710559776234</v>
       </c>
       <c r="C3" t="n">
-        <v>26.43355693684537</v>
+        <v>35.03366682604743</v>
       </c>
       <c r="D3" t="n">
-        <v>74.75027020135214</v>
+        <v>78.97669406813466</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.0606570401476</v>
+        <v>42.95931604243193</v>
       </c>
       <c r="C4" t="n">
-        <v>71.57333463040946</v>
+        <v>100.2256413788526</v>
       </c>
       <c r="D4" t="n">
-        <v>155.7817622144754</v>
+        <v>162.5970547773567</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.28311285838414</v>
+        <v>40.74252972624264</v>
       </c>
       <c r="C5" t="n">
-        <v>151.3854959948582</v>
+        <v>190.2381613904257</v>
       </c>
       <c r="D5" t="n">
-        <v>132.9286391550181</v>
+        <v>121.7858027118169</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.23278168356029</v>
+        <v>31.27553661419064</v>
       </c>
       <c r="C6" t="n">
-        <v>169.9022394446573</v>
+        <v>196.3475773539536</v>
       </c>
       <c r="D6" t="n">
-        <v>59.69320566131882</v>
+        <v>53.09193409796327</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>139.8352342543944</v>
+        <v>156.8430314827662</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>34.55457394637499</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>83.7823490804228</v>
+        <v>95.13135254151592</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.8390597964283</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2806,7 +2806,7 @@
         <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.241150082346221</v>
+        <v>3.107231483941155</v>
       </c>
       <c r="C2" t="n">
-        <v>8.030696220738909</v>
+        <v>6.196791509205867</v>
       </c>
       <c r="D2" t="n">
-        <v>18.29388672093506</v>
+        <v>18.6679325962531</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.40147805777471</v>
+        <v>15.19745446174063</v>
       </c>
       <c r="C3" t="n">
-        <v>20.49398332615217</v>
+        <v>26.73298998664065</v>
       </c>
       <c r="D3" t="n">
-        <v>67.74059159302992</v>
+        <v>70.46494147231481</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.0013512672653</v>
+        <v>40.75136545558085</v>
       </c>
       <c r="C4" t="n">
-        <v>68.68895987533233</v>
+        <v>93.83151858109315</v>
       </c>
       <c r="D4" t="n">
-        <v>157.3388140734108</v>
+        <v>164.2179202370682</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.93507544946203</v>
+        <v>50.9281621578033</v>
       </c>
       <c r="C5" t="n">
-        <v>143.2124463570035</v>
+        <v>189.2318699935727</v>
       </c>
       <c r="D5" t="n">
-        <v>154.4780012632356</v>
+        <v>145.5686408471958</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.37619896383834</v>
+        <v>40.8151790563569</v>
       </c>
       <c r="C6" t="n">
-        <v>206.2092330431128</v>
+        <v>245.2935908968826</v>
       </c>
       <c r="D6" t="n">
-        <v>82.27438460669971</v>
+        <v>72.09071567054754</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.13997331554657</v>
+        <v>17.42700349808513</v>
       </c>
       <c r="C7" t="n">
-        <v>187.6247490017207</v>
+        <v>214.1545172135822</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>40.18391528252619</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>128.5942230407684</v>
+        <v>141.6956461539421</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>58.90780749792134</v>
+        <v>65.34218195155493</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35.41654843070368</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.909900195387546</v>
+        <v>2.132356013624072</v>
       </c>
       <c r="C2" t="n">
-        <v>4.07228947721577</v>
+        <v>4.063453747877548</v>
       </c>
       <c r="D2" t="n">
-        <v>14.05862712481433</v>
+        <v>13.49412219487241</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.35591675275186</v>
+        <v>13.41067364001143</v>
       </c>
       <c r="C3" t="n">
-        <v>26.11448893296516</v>
+        <v>25.79051219056371</v>
       </c>
       <c r="D3" t="n">
-        <v>67.63259934556277</v>
+        <v>69.37520152060085</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.46607778427253</v>
+        <v>37.17780381212246</v>
       </c>
       <c r="C4" t="n">
-        <v>62.72876956284995</v>
+        <v>84.76998727089509</v>
       </c>
       <c r="D4" t="n">
-        <v>156.5858135842535</v>
+        <v>164.9198698456047</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.12008598621694</v>
+        <v>55.61600744558182</v>
       </c>
       <c r="C5" t="n">
-        <v>140.1935721664445</v>
+        <v>187.6119862815655</v>
       </c>
       <c r="D5" t="n">
-        <v>169.7932654494859</v>
+        <v>160.5157496443535</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.6680400739069</v>
+        <v>48.58374864006191</v>
       </c>
       <c r="C6" t="n">
-        <v>224.16147156297</v>
+        <v>275.6030877700944</v>
       </c>
       <c r="D6" t="n">
-        <v>97.65051715061327</v>
+        <v>87.7083581497058</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.48122060599696</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>231.9408403714217</v>
+        <v>265.6570017783699</v>
       </c>
       <c r="D7" t="n">
-        <v>48.32849423695774</v>
+        <v>44.91495746929157</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>165.812278508765</v>
+        <v>182.5019894809608</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>70.77811898996953</v>
+        <v>73.66249374504666</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>24.34439782220815</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.286310476741575</v>
+        <v>4.067380738694535</v>
       </c>
       <c r="C2" t="n">
-        <v>10.81296921457437</v>
+        <v>11.13203721845458</v>
       </c>
       <c r="D2" t="n">
-        <v>12.04015384488288</v>
+        <v>18.25756205587793</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.19959788359837</v>
+        <v>10.4948829583984</v>
       </c>
       <c r="C3" t="n">
-        <v>21.02903582496668</v>
+        <v>21.01430960940298</v>
       </c>
       <c r="D3" t="n">
-        <v>63.53380268033234</v>
+        <v>64.70208244838604</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.36098972218912</v>
+        <v>31.61325782445154</v>
       </c>
       <c r="C4" t="n">
-        <v>63.6987362946458</v>
+        <v>75.51701515836891</v>
       </c>
       <c r="D4" t="n">
-        <v>154.7735073222139</v>
+        <v>162.124834131614</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.21826075664162</v>
+        <v>55.54237636776331</v>
       </c>
       <c r="C5" t="n">
-        <v>129.0016483380309</v>
+        <v>173.7693436516855</v>
       </c>
       <c r="D5" t="n">
-        <v>183.5377333089412</v>
+        <v>176.6654993792135</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.05925868628265</v>
+        <v>58.44540432922113</v>
       </c>
       <c r="C6" t="n">
-        <v>224.483484809963</v>
+        <v>285.585498426876</v>
       </c>
       <c r="D6" t="n">
-        <v>120.6744643106095</v>
+        <v>108.4782125807513</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.77037851486003</v>
+        <v>29.58398531977338</v>
       </c>
       <c r="C7" t="n">
-        <v>273.9213539527195</v>
+        <v>321.8905285299229</v>
       </c>
       <c r="D7" t="n">
-        <v>60.18604300885071</v>
+        <v>54.49681506274045</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>222.8076414788136</v>
+        <v>246.7573767239145</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>122.6968645813578</v>
+        <v>128.9093640538316</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>51.24723016168351</v>
+        <v>51.38958357879929</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.060328578315561</v>
+        <v>4.496404485450391</v>
       </c>
       <c r="C2" t="n">
-        <v>5.561600744558181</v>
+        <v>9.08902024591697</v>
       </c>
       <c r="D2" t="n">
-        <v>7.552585088770712</v>
+        <v>9.601492547533805</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.033600406122644</v>
+        <v>2.938370878810703</v>
       </c>
       <c r="C2" t="n">
-        <v>6.054438092090079</v>
+        <v>6.412776004140166</v>
       </c>
       <c r="D2" t="n">
-        <v>8.861254778531711</v>
+        <v>13.58346123595887</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.59291886010284</v>
+        <v>14.50041359172539</v>
       </c>
       <c r="C3" t="n">
-        <v>30.73852061996763</v>
+        <v>30.62071089545801</v>
       </c>
       <c r="D3" t="n">
-        <v>68.27073535332319</v>
+        <v>71.41232800691299</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.52386203010285</v>
+        <v>42.84445156103505</v>
       </c>
       <c r="C4" t="n">
-        <v>87.41187034302325</v>
+        <v>106.3645097735079</v>
       </c>
       <c r="D4" t="n">
-        <v>161.6526134858713</v>
+        <v>166.7832269882651</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.07985002587604</v>
+        <v>33.94392687433348</v>
       </c>
       <c r="C5" t="n">
-        <v>190.0663555421825</v>
+        <v>249.9775091938441</v>
       </c>
       <c r="D5" t="n">
-        <v>169.9405276051229</v>
+        <v>159.6076330179252</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.82268888062561</v>
+        <v>18.35475507859837</v>
       </c>
       <c r="C6" t="n">
-        <v>228.7904119884937</v>
+        <v>265.1779088986975</v>
       </c>
       <c r="D6" t="n">
-        <v>93.22283500446015</v>
+        <v>84.36747071215392</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.186393195086651</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>156.663371652889</v>
+        <v>173.4915090513836</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>90.37478491444013</v>
+        <v>94.96445543179397</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03456645829366</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>39.160934174701</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.750497214401069</v>
+        <v>6.08781751403447</v>
       </c>
       <c r="C2" t="n">
-        <v>4.435536127787089</v>
+        <v>5.21111681414207</v>
       </c>
       <c r="D2" t="n">
-        <v>20.92006182979528</v>
+        <v>16.93220265514474</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.87071240267569</v>
+        <v>9.557313900842699</v>
       </c>
       <c r="C3" t="n">
-        <v>14.01444847812322</v>
+        <v>22.90417394007808</v>
       </c>
       <c r="D3" t="n">
-        <v>9.478774084502955</v>
+        <v>11.20174130545611</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39871072603525</v>
+        <v>13.3980213363327</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14619144806693</v>
+        <v>70.14258229021236</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576318908945324</v>
+        <v>1.576237804274435</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.80172802147115</v>
+        <v>4.618141200776996</v>
       </c>
       <c r="C2" t="n">
-        <v>4.746750150033328</v>
+        <v>4.773257338047992</v>
       </c>
       <c r="D2" t="n">
-        <v>36.25201572701772</v>
+        <v>17.5438314748905</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.1440802328128</v>
+        <v>16.4050041379642</v>
       </c>
       <c r="C3" t="n">
-        <v>16.06630117999905</v>
+        <v>21.28919896659208</v>
       </c>
       <c r="D3" t="n">
-        <v>24.75967710110456</v>
+        <v>22.71764187627119</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.9579080219044</v>
+        <v>11.23119373658351</v>
       </c>
       <c r="C4" t="n">
-        <v>21.88806506618264</v>
+        <v>35.4548365911693</v>
       </c>
       <c r="D4" t="n">
-        <v>20.0374706436774</v>
+        <v>20.9436237746972</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4419873726311</v>
+        <v>15.44058914308368</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15003481573139</v>
+        <v>86.14223416667737</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250944710027599</v>
+        <v>3.250650345912354</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.067781649322035</v>
+        <v>5.105088062083413</v>
       </c>
       <c r="C2" t="n">
-        <v>6.522731747015809</v>
+        <v>4.322635141798706</v>
       </c>
       <c r="D2" t="n">
-        <v>25.84647180970578</v>
+        <v>24.91970197689679</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.72545480017616</v>
+        <v>16.17920216598743</v>
       </c>
       <c r="C3" t="n">
-        <v>17.52419652080557</v>
+        <v>19.63986282345744</v>
       </c>
       <c r="D3" t="n">
-        <v>48.01237147619026</v>
+        <v>31.47974013667397</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.52918737478481</v>
+        <v>22.8707945181337</v>
       </c>
       <c r="C4" t="n">
-        <v>32.68532631748906</v>
+        <v>45.98408071921636</v>
       </c>
       <c r="D4" t="n">
-        <v>27.93759441975148</v>
+        <v>27.61852641587127</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.03270077387641</v>
+        <v>10.16108873895449</v>
       </c>
       <c r="C5" t="n">
-        <v>25.35363446217388</v>
+        <v>39.61351986635881</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>30.18874190558942</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73405944373458</v>
+        <v>16.73416413359425</v>
       </c>
       <c r="C21" t="n">
-        <v>102.077762606781</v>
+        <v>102.0784012149249</v>
       </c>
       <c r="D21" t="n">
-        <v>4.183514860933645</v>
+        <v>5.020249240078275</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.424156065963627</v>
+        <v>4.76442160870977</v>
       </c>
       <c r="C2" t="n">
-        <v>5.104106314379167</v>
+        <v>5.643085804010666</v>
       </c>
       <c r="D2" t="n">
-        <v>31.69670637931252</v>
+        <v>29.17656002251096</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5291052593268</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="C3" t="n">
-        <v>22.01078352921349</v>
+        <v>17.9758004647591</v>
       </c>
       <c r="D3" t="n">
-        <v>56.97572801596364</v>
+        <v>43.41288348179395</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.34524070119216</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="C4" t="n">
-        <v>38.92629647338603</v>
+        <v>47.75809882079034</v>
       </c>
       <c r="D4" t="n">
-        <v>44.75885958431633</v>
+        <v>36.66729500591412</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.02260555939346</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="C5" t="n">
-        <v>44.00684084286328</v>
+        <v>63.71542600561801</v>
       </c>
       <c r="D5" t="n">
-        <v>32.61856747360028</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.87423848286517</v>
+        <v>9.94215900090745</v>
       </c>
       <c r="C6" t="n">
-        <v>27.04911274740813</v>
+        <v>38.84284791852506</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>38.27932473628739</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -5560,7 +5560,7 @@
         <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05996132241334</v>
+        <v>18.05976980904205</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8197476747918</v>
+        <v>117.8184982780362</v>
       </c>
       <c r="D21" t="n">
-        <v>6.019987107471112</v>
+        <v>6.879912308206493</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.368597357449058</v>
+        <v>5.481097432809942</v>
       </c>
       <c r="C2" t="n">
-        <v>5.838453597155781</v>
+        <v>10.08647591343173</v>
       </c>
       <c r="D2" t="n">
-        <v>31.68885239767855</v>
+        <v>42.37812140151782</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.12520604225386</v>
+        <v>14.74585051778709</v>
       </c>
       <c r="C3" t="n">
-        <v>19.49750940634166</v>
+        <v>19.01154429273948</v>
       </c>
       <c r="D3" t="n">
-        <v>64.34374453633596</v>
+        <v>52.6167682091078</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.71313404837746</v>
+        <v>22.02845498788993</v>
       </c>
       <c r="C4" t="n">
-        <v>40.15151760828606</v>
+        <v>38.64551662997145</v>
       </c>
       <c r="D4" t="n">
-        <v>54.33089970072273</v>
+        <v>43.15075684476006</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.89926520155685</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="C5" t="n">
-        <v>43.51596699073988</v>
+        <v>56.67138622764714</v>
       </c>
       <c r="D5" t="n">
-        <v>32.83946070705581</v>
+        <v>30.85142160595602</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.16229147083699</v>
+        <v>10.82769543013807</v>
       </c>
       <c r="C6" t="n">
-        <v>33.52962934314132</v>
+        <v>48.46299367243955</v>
       </c>
       <c r="D6" t="n">
-        <v>31.03402667894593</v>
+        <v>31.15478164656829</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>19.3433750167749</v>
+        <v>24.79305652304895</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>29.84218496599028</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.058694006655058</v>
+        <v>7.058467333719006</v>
       </c>
       <c r="C21" t="n">
-        <v>66.17525631239117</v>
+        <v>66.17313125361568</v>
       </c>
       <c r="D21" t="n">
-        <v>4.411683754159411</v>
+        <v>5.293850500289254</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.231733515931253</v>
+        <v>5.475206946584461</v>
       </c>
       <c r="C2" t="n">
-        <v>4.425718650744621</v>
+        <v>6.293984531926301</v>
       </c>
       <c r="D2" t="n">
-        <v>27.77364255314226</v>
+        <v>31.25001117388022</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.95402208881642</v>
+        <v>17.52419652080557</v>
       </c>
       <c r="C3" t="n">
-        <v>21.8684301120977</v>
+        <v>32.16696352964674</v>
       </c>
       <c r="D3" t="n">
-        <v>75.41294990171875</v>
+        <v>75.50130719510095</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.83098483061608</v>
+        <v>26.50816976236813</v>
       </c>
       <c r="C4" t="n">
-        <v>45.29489383083509</v>
+        <v>44.36321525950487</v>
       </c>
       <c r="D4" t="n">
-        <v>74.9299300312293</v>
+        <v>60.30385273336033</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.38509144643879</v>
+        <v>27.63619787454772</v>
       </c>
       <c r="C5" t="n">
-        <v>62.66004722355269</v>
+        <v>65.82618356974865</v>
       </c>
       <c r="D5" t="n">
-        <v>46.26486056263094</v>
+        <v>40.39891802975625</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.66797365398211</v>
+        <v>19.76356303419254</v>
       </c>
       <c r="C6" t="n">
-        <v>54.90325861229863</v>
+        <v>72.57373554103698</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>34.41516577237194</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.49822911213864</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>36.65060529494193</v>
+        <v>51.62225778470578</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>23.11524969649115</v>
+        <v>27.28767743954009</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>30.95155987178918</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.281639007951384</v>
+        <v>7.280291412249395</v>
       </c>
       <c r="C21" t="n">
-        <v>75.5470047074956</v>
+        <v>75.53302340208748</v>
       </c>
       <c r="D21" t="n">
-        <v>5.461229255963538</v>
+        <v>6.37025498571822</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.423755155336128</v>
+        <v>4.720242962018665</v>
       </c>
       <c r="C2" t="n">
-        <v>4.925428232206248</v>
+        <v>4.541564879845745</v>
       </c>
       <c r="D2" t="n">
-        <v>20.07281356103028</v>
+        <v>32.09333245182823</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.92318699935727</v>
+        <v>18.34395585385165</v>
       </c>
       <c r="C3" t="n">
-        <v>19.05081420090935</v>
+        <v>27.51347941151686</v>
       </c>
       <c r="D3" t="n">
-        <v>80.1351563591459</v>
+        <v>82.98222470146165</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.42105625859742</v>
+        <v>30.98788453684632</v>
       </c>
       <c r="C4" t="n">
-        <v>50.46379549369455</v>
+        <v>65.67695791870312</v>
       </c>
       <c r="D4" t="n">
-        <v>95.89907924623694</v>
+        <v>84.57854646856697</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.82183030610837</v>
+        <v>34.18936380039518</v>
       </c>
       <c r="C5" t="n">
-        <v>74.95643721924398</v>
+        <v>75.103699374881</v>
       </c>
       <c r="D5" t="n">
-        <v>62.24280444924779</v>
+        <v>52.54804586981054</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.20761609614837</v>
+        <v>29.46421209985528</v>
       </c>
       <c r="C6" t="n">
-        <v>79.98004022187492</v>
+        <v>89.68068928753766</v>
       </c>
       <c r="D6" t="n">
-        <v>41.66046382971341</v>
+        <v>39.72838434775569</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>60.42558944868693</v>
+        <v>81.38590293435632</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>37.30150402285756</v>
+        <v>49.98568436172635</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>26.62499773917349</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.493024901398335</v>
+        <v>7.489825535770415</v>
       </c>
       <c r="C21" t="n">
-        <v>85.23315825340605</v>
+        <v>85.19676546938848</v>
       </c>
       <c r="D21" t="n">
-        <v>6.556396788723543</v>
+        <v>7.489825535770415</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_84_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_84_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497623298814</v>
+        <v>10.84497625363284</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907159615558</v>
+        <v>37.78907166809156</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.858669388317464</v>
+        <v>5.566509483079415</v>
       </c>
       <c r="C2" t="n">
-        <v>10.24748253692821</v>
+        <v>6.244897146713961</v>
       </c>
       <c r="D2" t="n">
-        <v>27.98766355266807</v>
+        <v>31.94017980996573</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.09222753093697</v>
+        <v>14.19607180340888</v>
       </c>
       <c r="C3" t="n">
-        <v>21.95678740547991</v>
+        <v>19.29134238844982</v>
       </c>
       <c r="D3" t="n">
-        <v>88.42601572151021</v>
+        <v>82.52080328046566</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.06820792214531</v>
+        <v>30.03068052520568</v>
       </c>
       <c r="C4" t="n">
-        <v>66.71073825127502</v>
+        <v>63.35414285045516</v>
       </c>
       <c r="D4" t="n">
-        <v>103.8502539029318</v>
+        <v>88.35631163450869</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.64435495581795</v>
+        <v>39.56443248114646</v>
       </c>
       <c r="C5" t="n">
-        <v>99.57376090323277</v>
+        <v>96.33399347921829</v>
       </c>
       <c r="D5" t="n">
-        <v>69.97406762019142</v>
+        <v>65.89981464756715</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.79630486579796</v>
+        <v>39.7686360036298</v>
       </c>
       <c r="C6" t="n">
-        <v>105.0970734873253</v>
+        <v>110.4907953744573</v>
       </c>
       <c r="D6" t="n">
-        <v>46.36990756698535</v>
+        <v>47.69821221083129</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.99078872223005</v>
+        <v>28.7455727803466</v>
       </c>
       <c r="C7" t="n">
-        <v>105.5202067478557</v>
+        <v>114.2636518018778</v>
       </c>
       <c r="D7" t="n">
-        <v>38.92629647338602</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.51866588747858</v>
+        <v>15.52143120414207</v>
       </c>
       <c r="C8" t="n">
-        <v>79.77681844709581</v>
+        <v>84.19959185472769</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>47.03749600587317</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
         <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.685047384423157</v>
+        <v>7.682993771483339</v>
       </c>
       <c r="C21" t="n">
-        <v>94.14183045918368</v>
+        <v>93.15629947923549</v>
       </c>
       <c r="D21" t="n">
-        <v>8.645678307476052</v>
+        <v>7.682993771483339</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.865361695797945</v>
+        <v>6.001423716060751</v>
       </c>
       <c r="C2" t="n">
-        <v>5.704935909378215</v>
+        <v>10.27497147264712</v>
       </c>
       <c r="D2" t="n">
-        <v>24.43177336788612</v>
+        <v>32.2710287862969</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.6062624173348</v>
+        <v>16.36573422979433</v>
       </c>
       <c r="C3" t="n">
-        <v>31.03304493124168</v>
+        <v>21.74571164906685</v>
       </c>
       <c r="D3" t="n">
-        <v>89.48630324209677</v>
+        <v>87.46881170986957</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.80019079888594</v>
+        <v>28.55020498720149</v>
       </c>
       <c r="C4" t="n">
-        <v>60.69949705817179</v>
+        <v>55.08390018988003</v>
       </c>
       <c r="D4" t="n">
-        <v>121.2586041946363</v>
+        <v>105.4073057618673</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.57134577280519</v>
+        <v>41.96971435655115</v>
       </c>
       <c r="C5" t="n">
-        <v>109.7593933347934</v>
+        <v>106.3232763699296</v>
       </c>
       <c r="D5" t="n">
-        <v>87.0810213666921</v>
+        <v>80.87146713733101</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.64537776125121</v>
+        <v>46.12839763174064</v>
       </c>
       <c r="C6" t="n">
-        <v>130.294610064524</v>
+        <v>129.7310868822863</v>
       </c>
       <c r="D6" t="n">
-        <v>56.23156325614456</v>
+        <v>56.31206656789281</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.09355343600648</v>
+        <v>37.4890178343687</v>
       </c>
       <c r="C7" t="n">
-        <v>126.8398398932794</v>
+        <v>136.7810171464826</v>
       </c>
       <c r="D7" t="n">
-        <v>42.51949307092936</v>
+        <v>43.59745205019235</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.11110172149591</v>
+        <v>22.94835258676919</v>
       </c>
       <c r="C8" t="n">
-        <v>108.7334669838555</v>
+        <v>115.6596970373167</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>11.31562403914873</v>
       </c>
       <c r="C9" t="n">
-        <v>70.11249404649018</v>
+        <v>74.32811868852599</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>42.56367171762047</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.865483266311561</v>
+        <v>7.864464138818037</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2512824620503</v>
+        <v>101.2549757872822</v>
       </c>
       <c r="D21" t="n">
-        <v>9.83185408288945</v>
+        <v>8.847522156170292</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.08272884906399</v>
+        <v>6.111379458936394</v>
       </c>
       <c r="C2" t="n">
-        <v>13.08669689760998</v>
+        <v>9.63094497866121</v>
       </c>
       <c r="D2" t="n">
-        <v>22.56939797292992</v>
+        <v>41.25107503704248</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.20298509506761</v>
+        <v>17.76472470834603</v>
       </c>
       <c r="C3" t="n">
-        <v>26.58081909248239</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D3" t="n">
-        <v>87.79769719079225</v>
+        <v>91.18472677044375</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.57496966398591</v>
+        <v>29.09900195387546</v>
       </c>
       <c r="C4" t="n">
-        <v>68.25502739005525</v>
+        <v>54.05011985730815</v>
       </c>
       <c r="D4" t="n">
-        <v>134.6722230777605</v>
+        <v>120.9395361907561</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.24031687002478</v>
+        <v>42.11697651218817</v>
       </c>
       <c r="C5" t="n">
-        <v>109.3666942530947</v>
+        <v>103.9179944945249</v>
       </c>
       <c r="D5" t="n">
-        <v>104.6297615801038</v>
+        <v>95.18043992672828</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.1258943569844</v>
+        <v>50.59633143376788</v>
       </c>
       <c r="C6" t="n">
-        <v>148.3273518961294</v>
+        <v>145.7109942643116</v>
       </c>
       <c r="D6" t="n">
-        <v>67.94479511551327</v>
+        <v>66.53598715991909</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.05847256056086</v>
+        <v>45.39405034896402</v>
       </c>
       <c r="C7" t="n">
-        <v>154.3277938644858</v>
+        <v>159.8373619807189</v>
       </c>
       <c r="D7" t="n">
-        <v>47.31042186765379</v>
+        <v>48.20872101703962</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.53802310412303</v>
+        <v>30.29182541453534</v>
       </c>
       <c r="C8" t="n">
-        <v>134.268724771315</v>
+        <v>143.7818600254666</v>
       </c>
       <c r="D8" t="n">
-        <v>40.63944621729671</v>
+        <v>41.0566889916016</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.31093628480575</v>
+        <v>16.19687362466387</v>
       </c>
       <c r="C9" t="n">
-        <v>97.84686669146257</v>
+        <v>103.8374911827766</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>60.07314202286233</v>
+        <v>62.35079669671494</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.626282586514</v>
+        <v>39.98167525545134</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>36.45032876327558</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1570,7 +1570,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>27.3485457972034</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.031066363841866</v>
+        <v>8.030834673315006</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4271625028257</v>
+        <v>109.420122423917</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04271625028256</v>
+        <v>10.03854334164376</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.291440199441061</v>
+        <v>5.652903281053134</v>
       </c>
       <c r="C2" t="n">
-        <v>8.898561191293089</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="D2" t="n">
-        <v>18.72978270162065</v>
+        <v>33.70045344368026</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.61455836732528</v>
+        <v>20.88668240785089</v>
       </c>
       <c r="C3" t="n">
-        <v>43.9528447191297</v>
+        <v>43.12817664756238</v>
       </c>
       <c r="D3" t="n">
-        <v>96.82486733134168</v>
+        <v>97.87533737488576</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.20713307006285</v>
+        <v>20.22891144600553</v>
       </c>
       <c r="C4" t="n">
-        <v>92.59353472603793</v>
+        <v>81.96218883674922</v>
       </c>
       <c r="D4" t="n">
-        <v>125.5085900063207</v>
+        <v>114.3156844302029</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.35425635697964</v>
+        <v>28.49522711576368</v>
       </c>
       <c r="C5" t="n">
-        <v>88.62727400088082</v>
+        <v>87.05647767408593</v>
       </c>
       <c r="D5" t="n">
-        <v>68.72233929727673</v>
+        <v>65.33530971762524</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.72709950041517</v>
+        <v>28.17615911188346</v>
       </c>
       <c r="C6" t="n">
-        <v>101.6354310821511</v>
+        <v>105.2580801108218</v>
       </c>
       <c r="D6" t="n">
-        <v>31.15478164656829</v>
+        <v>31.71830482880595</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.20552942755285</v>
+        <v>20.06201433628357</v>
       </c>
       <c r="C7" t="n">
-        <v>94.38129729547136</v>
+        <v>101.0885976108856</v>
       </c>
       <c r="D7" t="n">
-        <v>28.56591295046944</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>72.09955139988574</v>
+        <v>76.52232480751763</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>47.59218345877262</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1867,7 +1867,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
         <v>22.63419332141022</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.354051068334604</v>
+        <v>3.538218726105504</v>
       </c>
       <c r="C2" t="n">
-        <v>4.433572632378596</v>
+        <v>2.889283493598362</v>
       </c>
       <c r="D2" t="n">
-        <v>13.29580915861455</v>
+        <v>23.02787415081318</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.38170423496954</v>
+        <v>20.78850763742621</v>
       </c>
       <c r="C3" t="n">
-        <v>40.02585390214246</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D3" t="n">
-        <v>90.81166264282996</v>
+        <v>101.8415981000429</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.21761349964007</v>
+        <v>28.65230674844316</v>
       </c>
       <c r="C4" t="n">
-        <v>104.411813589761</v>
+        <v>97.59652102687967</v>
       </c>
       <c r="D4" t="n">
-        <v>143.4912627050096</v>
+        <v>134.5573585963636</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.42221793275092</v>
+        <v>31.17048960983623</v>
       </c>
       <c r="C5" t="n">
-        <v>127.9462695559656</v>
+        <v>118.5460352878024</v>
       </c>
       <c r="D5" t="n">
-        <v>89.48630324209678</v>
+        <v>83.86579763528378</v>
       </c>
     </row>
     <row r="6">
@@ -2080,10 +2080,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.16107304342126</v>
+        <v>33.00635781677777</v>
       </c>
       <c r="C6" t="n">
-        <v>121.9222656427072</v>
+        <v>123.572583533546</v>
       </c>
       <c r="D6" t="n">
         <v>39.48687441251096</v>
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.18745705824891</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="C7" t="n">
-        <v>118.2161680591754</v>
+        <v>125.1630148144258</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>92.04375601165971</v>
+        <v>97.88515485192822</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>28.12216298814988</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>52.14062057254808</v>
+        <v>54.0265579124062</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
+        <v>29.852984190737</v>
+      </c>
+      <c r="D11" t="n">
         <v>29.49759152179966</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
         <v>20.82875929330033</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.950953672516665</v>
+        <v>3.816053326407352</v>
       </c>
       <c r="C2" t="n">
-        <v>10.27595322035137</v>
+        <v>4.255876297909923</v>
       </c>
       <c r="D2" t="n">
-        <v>14.24319569321272</v>
+        <v>19.07143090269854</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.53677931451153</v>
+        <v>16.35591675275186</v>
       </c>
       <c r="C3" t="n">
-        <v>28.04853191033137</v>
+        <v>22.3445777486574</v>
       </c>
       <c r="D3" t="n">
-        <v>81.92684591939633</v>
+        <v>97.72316648072751</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.90077103307561</v>
+        <v>34.22961545626929</v>
       </c>
       <c r="C4" t="n">
-        <v>102.0634730812026</v>
+        <v>91.99368687874312</v>
       </c>
       <c r="D4" t="n">
-        <v>154.2374730756951</v>
+        <v>151.7104544849638</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.09810232162923</v>
+        <v>36.71736413883072</v>
       </c>
       <c r="C5" t="n">
-        <v>159.5340019401067</v>
+        <v>148.5875150377548</v>
       </c>
       <c r="D5" t="n">
-        <v>115.4044426342126</v>
+        <v>108.1640533153924</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.59504658642736</v>
+        <v>37.43403996293088</v>
       </c>
       <c r="C6" t="n">
-        <v>161.5701466787146</v>
+        <v>155.5323982975967</v>
       </c>
       <c r="D6" t="n">
-        <v>54.37998708593508</v>
+        <v>53.05168244208915</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.81112889235289</v>
+        <v>27.36818075128833</v>
       </c>
       <c r="C7" t="n">
-        <v>146.5425345698086</v>
+        <v>150.3752776071882</v>
       </c>
       <c r="D7" t="n">
-        <v>34.55457394637499</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>13.51866588747858</v>
       </c>
       <c r="C8" t="n">
-        <v>122.0852357616121</v>
+        <v>130.263194137988</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>78.76561831172157</v>
+        <v>84.09061785955626</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>45.55309347705201</v>
+        <v>46.40721397974673</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
         <v>25.38505038870978</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2579,7 +2579,7 @@
         <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.911863690796039</v>
+        <v>2.263910205993145</v>
       </c>
       <c r="C2" t="n">
-        <v>4.790928796724435</v>
+        <v>1.997856578142259</v>
       </c>
       <c r="D2" t="n">
-        <v>9.969647936626359</v>
+        <v>13.1750541909922</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.05710559776234</v>
+        <v>16.40991287648544</v>
       </c>
       <c r="C3" t="n">
-        <v>35.03366682604743</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D3" t="n">
-        <v>78.97669406813466</v>
+        <v>95.11171758743099</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.95931604243193</v>
+        <v>37.75212621910685</v>
       </c>
       <c r="C4" t="n">
-        <v>100.2256413788526</v>
+        <v>88.39459979497431</v>
       </c>
       <c r="D4" t="n">
-        <v>162.5970547773567</v>
+        <v>166.1961418611255</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.74252972624264</v>
+        <v>38.9508401659922</v>
       </c>
       <c r="C5" t="n">
-        <v>190.2381613904257</v>
+        <v>176.0764507566655</v>
       </c>
       <c r="D5" t="n">
-        <v>121.7858027118169</v>
+        <v>114.6681318560275</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.27553661419064</v>
+        <v>32.20132469929539</v>
       </c>
       <c r="C6" t="n">
-        <v>196.3475773539536</v>
+        <v>190.5110872522063</v>
       </c>
       <c r="D6" t="n">
-        <v>53.09193409796327</v>
+        <v>52.00513938936205</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.024805734513427</v>
+        <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>156.8430314827662</v>
+        <v>162.4723728189174</v>
       </c>
       <c r="D7" t="n">
-        <v>34.55457394637499</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>95.13135254151592</v>
+        <v>102.808619588726</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>34.72343455150543</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,7 +2772,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
         <v>20.25738212942868</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2876,7 +2876,7 @@
         <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.107231483941155</v>
+        <v>2.357176237896592</v>
       </c>
       <c r="C2" t="n">
-        <v>6.196791509205867</v>
+        <v>6.970408700152354</v>
       </c>
       <c r="D2" t="n">
-        <v>18.6679325962531</v>
+        <v>13.15443748920301</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.19745446174063</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C3" t="n">
-        <v>26.73298998664065</v>
+        <v>14.27952035826986</v>
       </c>
       <c r="D3" t="n">
-        <v>70.46494147231481</v>
+        <v>84.73955309206343</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.75136545558085</v>
+        <v>35.12300586713388</v>
       </c>
       <c r="C4" t="n">
-        <v>93.83151858109315</v>
+        <v>71.49675830947821</v>
       </c>
       <c r="D4" t="n">
-        <v>164.2179202370682</v>
+        <v>174.3770454806142</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.9281621578033</v>
+        <v>46.73119072214818</v>
       </c>
       <c r="C5" t="n">
-        <v>189.2318699935727</v>
+        <v>171.3395180836746</v>
       </c>
       <c r="D5" t="n">
-        <v>145.5686408471958</v>
+        <v>143.7524075943392</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.8151790563569</v>
+        <v>40.57366912111219</v>
       </c>
       <c r="C6" t="n">
-        <v>245.2935908968826</v>
+        <v>232.0910477701715</v>
       </c>
       <c r="D6" t="n">
-        <v>72.09071567054754</v>
+        <v>69.59511300635215</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>18.32530264747096</v>
       </c>
       <c r="C7" t="n">
         <v>214.1545172135822</v>
       </c>
       <c r="D7" t="n">
-        <v>40.18391528252619</v>
+        <v>40.24380189248525</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>141.6956461539421</v>
+        <v>149.5398103108741</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>32.7952820603647</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>65.34218195155493</v>
+        <v>69.11405663127118</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3075,7 +3075,7 @@
         <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,7 +3083,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
         <v>23.98900515327081</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3173,7 +3173,7 @@
         <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.132356013624072</v>
+        <v>1.614974973486003</v>
       </c>
       <c r="C2" t="n">
-        <v>4.063453747877548</v>
+        <v>3.454770171244526</v>
       </c>
       <c r="D2" t="n">
-        <v>13.49412219487241</v>
+        <v>10.78548027885546</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.41067364001143</v>
+        <v>10.50470043544087</v>
       </c>
       <c r="C3" t="n">
-        <v>25.79051219056371</v>
+        <v>20.35653864755761</v>
       </c>
       <c r="D3" t="n">
-        <v>69.37520152060085</v>
+        <v>77.85259294677206</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.17780381212246</v>
+        <v>31.34524070119216</v>
       </c>
       <c r="C4" t="n">
-        <v>84.76998727089509</v>
+        <v>57.8789359038707</v>
       </c>
       <c r="D4" t="n">
-        <v>164.9198698456047</v>
+        <v>176.9168267915007</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.61600744558182</v>
+        <v>50.78090000216628</v>
       </c>
       <c r="C5" t="n">
-        <v>187.6119862815655</v>
+        <v>161.9883712007237</v>
       </c>
       <c r="D5" t="n">
-        <v>160.5157496443535</v>
+        <v>164.197303535279</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.58374864006191</v>
+        <v>47.21519234034186</v>
       </c>
       <c r="C6" t="n">
-        <v>275.6030877700944</v>
+        <v>256.8860677886289</v>
       </c>
       <c r="D6" t="n">
-        <v>87.7083581497058</v>
+        <v>84.44797402390215</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.75017841923158</v>
+        <v>17.12757044828985</v>
       </c>
       <c r="C7" t="n">
-        <v>265.6570017783699</v>
+        <v>260.8660729816455</v>
       </c>
       <c r="D7" t="n">
-        <v>44.91495746929157</v>
+        <v>45.8132566186774</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>182.5019894809608</v>
+        <v>188.0095941017854</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>73.66249374504666</v>
+        <v>79.87499321752047</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3470,7 +3470,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.067380738694535</v>
+        <v>3.237803928605981</v>
       </c>
       <c r="C2" t="n">
-        <v>11.13203721845458</v>
+        <v>16.94791061841268</v>
       </c>
       <c r="D2" t="n">
-        <v>18.25756205587793</v>
+        <v>16.89391449467911</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.4948829583984</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C3" t="n">
-        <v>21.01430960940298</v>
+        <v>16.96460032938488</v>
       </c>
       <c r="D3" t="n">
-        <v>64.70208244838604</v>
+        <v>69.99861131279758</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.61325782445154</v>
+        <v>25.99766095615978</v>
       </c>
       <c r="C4" t="n">
-        <v>75.51701515836891</v>
+        <v>54.53510322320607</v>
       </c>
       <c r="D4" t="n">
-        <v>162.124834131614</v>
+        <v>175.2066222907028</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.54237636776331</v>
+        <v>49.3573658310084</v>
       </c>
       <c r="C5" t="n">
-        <v>173.7693436516855</v>
+        <v>137.6901155206152</v>
       </c>
       <c r="D5" t="n">
-        <v>176.6654993792135</v>
+        <v>181.2797135891736</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.44540432922113</v>
+        <v>55.58753676215866</v>
       </c>
       <c r="C6" t="n">
-        <v>285.585498426876</v>
+        <v>258.0936174648525</v>
       </c>
       <c r="D6" t="n">
-        <v>108.4782125807513</v>
+        <v>108.1561993337584</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.58398531977338</v>
+        <v>30.48228446915921</v>
       </c>
       <c r="C7" t="n">
-        <v>321.8905285299229</v>
+        <v>309.6736600982757</v>
       </c>
       <c r="D7" t="n">
-        <v>54.49681506274045</v>
+        <v>55.51488743204438</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>246.7573767239145</v>
+        <v>249.8449732537707</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>128.9093640538316</v>
+        <v>137.2296758473234</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>54.52135875534661</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
         <v>11.36962016288231</v>
@@ -3781,7 +3781,7 @@
         <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.496404485450391</v>
+        <v>5.824709129296326</v>
       </c>
       <c r="C2" t="n">
-        <v>9.08902024591697</v>
+        <v>9.101782966072179</v>
       </c>
       <c r="D2" t="n">
-        <v>9.601492547533805</v>
+        <v>13.97223332684061</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.938370878810703</v>
+        <v>2.314961086613979</v>
       </c>
       <c r="C2" t="n">
-        <v>6.412776004140166</v>
+        <v>9.627017987844223</v>
       </c>
       <c r="D2" t="n">
-        <v>13.58346123595887</v>
+        <v>12.43383467428585</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.50041359172539</v>
+        <v>11.48644813968768</v>
       </c>
       <c r="C3" t="n">
-        <v>30.62071089545801</v>
+        <v>34.1500938922253</v>
       </c>
       <c r="D3" t="n">
-        <v>71.41232800691299</v>
+        <v>77.13100838415066</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.84445156103505</v>
+        <v>36.94807484932871</v>
       </c>
       <c r="C4" t="n">
-        <v>106.3645097735079</v>
+        <v>79.00123776074084</v>
       </c>
       <c r="D4" t="n">
-        <v>166.7832269882651</v>
+        <v>178.1420479264007</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.94392687433348</v>
+        <v>32.66765485881262</v>
       </c>
       <c r="C5" t="n">
-        <v>249.9775091938441</v>
+        <v>213.2601450550134</v>
       </c>
       <c r="D5" t="n">
-        <v>159.6076330179252</v>
+        <v>164.5654589243716</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.35475507859837</v>
+        <v>18.91827826083604</v>
       </c>
       <c r="C6" t="n">
-        <v>265.1779088986975</v>
+        <v>254.55147174793</v>
       </c>
       <c r="D6" t="n">
-        <v>84.36747071215392</v>
+        <v>84.7699872708951</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>173.4915090513836</v>
+        <v>175.7073136198686</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>94.96445543179397</v>
+        <v>101.1396484915064</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.95111790343269</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>41.60155896745857</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.20713307006285</v>
+        <v>22.49183990429443</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.34806277111788</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
         <v>9.365873098514571</v>
@@ -4389,7 +4389,7 @@
         <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.08781751403447</v>
+        <v>6.384305320717008</v>
       </c>
       <c r="C2" t="n">
-        <v>5.21111681414207</v>
+        <v>6.780931393232719</v>
       </c>
       <c r="D2" t="n">
-        <v>16.93220265514474</v>
+        <v>18.91435127001905</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.557313900842699</v>
+        <v>12.37492981203104</v>
       </c>
       <c r="C3" t="n">
-        <v>22.90417394007808</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D3" t="n">
-        <v>11.20174130545611</v>
+        <v>14.87347771933918</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3980213363327</v>
+        <v>13.39704200765981</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14258229021236</v>
+        <v>70.13745521657195</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576237804274435</v>
+        <v>1.576122589136448</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.618141200776996</v>
+        <v>4.819399480147592</v>
       </c>
       <c r="C2" t="n">
-        <v>4.773257338047992</v>
+        <v>3.784637399871454</v>
       </c>
       <c r="D2" t="n">
-        <v>17.5438314748905</v>
+        <v>17.50750680983337</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.4050041379642</v>
+        <v>18.18687622117216</v>
       </c>
       <c r="C3" t="n">
-        <v>21.28919896659208</v>
+        <v>25.12783249019711</v>
       </c>
       <c r="D3" t="n">
-        <v>22.71764187627119</v>
+        <v>27.16495897650924</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.23119373658351</v>
+        <v>14.40911105523044</v>
       </c>
       <c r="C4" t="n">
-        <v>35.4548365911693</v>
+        <v>35.49312475163494</v>
       </c>
       <c r="D4" t="n">
-        <v>20.9436237746972</v>
+        <v>22.8707945181337</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4896,7 +4896,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44058914308368</v>
+        <v>15.43752024135479</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14223416667737</v>
+        <v>86.12511292545307</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250650345912354</v>
+        <v>3.250004261337852</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.105088062083413</v>
+        <v>4.396266219617217</v>
       </c>
       <c r="C2" t="n">
-        <v>4.322635141798706</v>
+        <v>5.786420968830701</v>
       </c>
       <c r="D2" t="n">
-        <v>24.91970197689679</v>
+        <v>16.13796876240907</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.17920216598743</v>
+        <v>17.34748193404114</v>
       </c>
       <c r="C3" t="n">
-        <v>19.63986282345744</v>
+        <v>18.82010349041136</v>
       </c>
       <c r="D3" t="n">
-        <v>31.47974013667397</v>
+        <v>34.86676971632547</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.8707945181337</v>
+        <v>26.24015263910875</v>
       </c>
       <c r="C4" t="n">
-        <v>45.98408071921636</v>
+        <v>51.65072846812894</v>
       </c>
       <c r="D4" t="n">
-        <v>27.61852641587127</v>
+        <v>31.33247798103695</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.16108873895449</v>
+        <v>12.61545799957152</v>
       </c>
       <c r="C5" t="n">
-        <v>39.61351986635881</v>
+        <v>39.71169463678348</v>
       </c>
       <c r="D5" t="n">
-        <v>30.18874190558942</v>
+        <v>30.87596529856219</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.01453059358123</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73416413359425</v>
+        <v>16.72818586606672</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0784012149249</v>
+        <v>102.041933783007</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020249240078275</v>
+        <v>4.182046466516679</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.76442160870977</v>
+        <v>4.569053815564656</v>
       </c>
       <c r="C2" t="n">
-        <v>5.643085804010666</v>
+        <v>5.098215828153687</v>
       </c>
       <c r="D2" t="n">
-        <v>29.17656002251096</v>
+        <v>17.64396974072368</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.90078672860884</v>
+        <v>16.24301576676348</v>
       </c>
       <c r="C3" t="n">
-        <v>17.9758004647591</v>
+        <v>20.90631736193583</v>
       </c>
       <c r="D3" t="n">
-        <v>43.41288348179395</v>
+        <v>39.37299167881833</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.55471281509523</v>
+        <v>29.96686692442964</v>
       </c>
       <c r="C4" t="n">
-        <v>47.75809882079034</v>
+        <v>49.11094715724244</v>
       </c>
       <c r="D4" t="n">
-        <v>36.66729500591412</v>
+        <v>41.19806066101315</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.11386703815941</v>
+        <v>25.86905200690346</v>
       </c>
       <c r="C5" t="n">
-        <v>63.71542600561801</v>
+        <v>69.4095626902495</v>
       </c>
       <c r="D5" t="n">
-        <v>32.93763547748049</v>
+        <v>34.70478134512475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.94215900090745</v>
+        <v>11.59247689174634</v>
       </c>
       <c r="C6" t="n">
-        <v>38.84284791852506</v>
+        <v>39.00385454202154</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.2097595180061</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
         <v>33.22921454564179</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05976980904205</v>
+        <v>18.0513798257107</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8184982780362</v>
+        <v>117.7637636248745</v>
       </c>
       <c r="D21" t="n">
-        <v>6.879912308206493</v>
+        <v>6.017126608570232</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.481097432809942</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C2" t="n">
-        <v>10.08647591343173</v>
+        <v>8.532369297609028</v>
       </c>
       <c r="D2" t="n">
-        <v>42.37812140151782</v>
+        <v>31.39727332951724</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.74585051778709</v>
+        <v>14.15680189523901</v>
       </c>
       <c r="C3" t="n">
-        <v>19.01154429273948</v>
+        <v>19.04590546238812</v>
       </c>
       <c r="D3" t="n">
-        <v>52.6167682091078</v>
+        <v>41.41993564217293</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.02845498788993</v>
+        <v>22.27094667083889</v>
       </c>
       <c r="C4" t="n">
-        <v>38.64551662997145</v>
+        <v>42.58919715793088</v>
       </c>
       <c r="D4" t="n">
-        <v>43.15075684476006</v>
+        <v>44.55465606183299</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.61041039233004</v>
+        <v>21.89297380470387</v>
       </c>
       <c r="C5" t="n">
-        <v>56.67138622764714</v>
+        <v>59.5920856477814</v>
       </c>
       <c r="D5" t="n">
-        <v>30.85142160595602</v>
+        <v>33.20761609614836</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.82769543013807</v>
+        <v>12.67927160034756</v>
       </c>
       <c r="C6" t="n">
-        <v>48.46299367243955</v>
+        <v>51.6831261423691</v>
       </c>
       <c r="D6" t="n">
-        <v>31.15478164656829</v>
+        <v>31.63780151705772</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>24.79305652304895</v>
+        <v>24.852943133008</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.058467333719006</v>
+        <v>7.054768158415524</v>
       </c>
       <c r="C21" t="n">
-        <v>66.17313125361568</v>
+        <v>66.13845148514552</v>
       </c>
       <c r="D21" t="n">
-        <v>5.293850500289254</v>
+        <v>4.409230099009702</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.475206946584461</v>
+        <v>4.454189334167778</v>
       </c>
       <c r="C2" t="n">
-        <v>6.293984531926301</v>
+        <v>6.408849013323178</v>
       </c>
       <c r="D2" t="n">
-        <v>31.25001117388022</v>
+        <v>32.68434456978481</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.52419652080557</v>
+        <v>16.67989349515331</v>
       </c>
       <c r="C3" t="n">
-        <v>32.16696352964674</v>
+        <v>28.26451640526567</v>
       </c>
       <c r="D3" t="n">
-        <v>75.50130719510095</v>
+        <v>57.78566987196726</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.50816976236813</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="C4" t="n">
-        <v>44.36321525950487</v>
+        <v>45.88197895797468</v>
       </c>
       <c r="D4" t="n">
-        <v>60.30385273336033</v>
+        <v>55.49230723484671</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.63619787454772</v>
+        <v>28.71612034921921</v>
       </c>
       <c r="C5" t="n">
-        <v>65.82618356974865</v>
+        <v>70.83309686140738</v>
       </c>
       <c r="D5" t="n">
-        <v>40.39891802975625</v>
+        <v>42.7551125199486</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.76356303419254</v>
+        <v>22.66168225712913</v>
       </c>
       <c r="C6" t="n">
-        <v>72.57373554103698</v>
+        <v>77.56494086942776</v>
       </c>
       <c r="D6" t="n">
-        <v>34.41516577237194</v>
+        <v>35.54221213684728</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.701630813366979</v>
+        <v>11.13890945238431</v>
       </c>
       <c r="C7" t="n">
-        <v>51.62225778470578</v>
+        <v>54.37704184282233</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -6151,7 +6151,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
         <v>27.28767743954009</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.280291412249395</v>
+        <v>7.2771359268414</v>
       </c>
       <c r="C21" t="n">
-        <v>75.53302340208748</v>
+        <v>75.50028524097954</v>
       </c>
       <c r="D21" t="n">
-        <v>6.37025498571822</v>
+        <v>5.457851945131051</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.720242962018665</v>
+        <v>3.729659528433633</v>
       </c>
       <c r="C2" t="n">
-        <v>4.541564879845745</v>
+        <v>3.615776794741003</v>
       </c>
       <c r="D2" t="n">
-        <v>32.09333245182823</v>
+        <v>35.53632165062179</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.34395585385165</v>
+        <v>15.97794388661684</v>
       </c>
       <c r="C3" t="n">
-        <v>27.51347941151686</v>
+        <v>26.24702487303848</v>
       </c>
       <c r="D3" t="n">
-        <v>82.98222470146165</v>
+        <v>70.52384633456963</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.98788453684632</v>
+        <v>29.57122259961817</v>
       </c>
       <c r="C4" t="n">
-        <v>65.67695791870312</v>
+        <v>60.5591071364645</v>
       </c>
       <c r="D4" t="n">
-        <v>84.57854646856697</v>
+        <v>71.99450439553134</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.18936380039518</v>
+        <v>34.68023765251858</v>
       </c>
       <c r="C5" t="n">
-        <v>75.103699374881</v>
+        <v>78.85888434362505</v>
       </c>
       <c r="D5" t="n">
-        <v>52.54804586981054</v>
+        <v>52.69530802544756</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.46421209985528</v>
+        <v>31.51704654943536</v>
       </c>
       <c r="C6" t="n">
-        <v>89.68068928753766</v>
+        <v>96.2819608508932</v>
       </c>
       <c r="D6" t="n">
-        <v>39.72838434775569</v>
+        <v>41.33845058272045</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="C7" t="n">
-        <v>81.38590293435632</v>
+        <v>86.59603800079415</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>49.98568436172635</v>
+        <v>51.90500112352886</v>
       </c>
       <c r="D8" t="n">
         <v>34.21390749300134</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
         <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6633,7 +6633,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.489825535770415</v>
+        <v>7.487033446469869</v>
       </c>
       <c r="C21" t="n">
-        <v>85.19676546938848</v>
+        <v>84.22912627278603</v>
       </c>
       <c r="D21" t="n">
-        <v>7.489825535770415</v>
+        <v>6.551154265661136</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_84_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_84_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497625363284</v>
+        <v>10.84497623707962</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907166809156</v>
+        <v>37.78907161041225</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.566509483079415</v>
+        <v>0.8806276907093888</v>
       </c>
       <c r="C2" t="n">
-        <v>6.244897146713961</v>
+        <v>4.486587008407923</v>
       </c>
       <c r="D2" t="n">
-        <v>31.94017980996573</v>
+        <v>20.00212772632451</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.19607180340888</v>
+        <v>8.148505945248527</v>
       </c>
       <c r="C3" t="n">
-        <v>19.29134238844982</v>
+        <v>47.28096943652639</v>
       </c>
       <c r="D3" t="n">
-        <v>82.52080328046566</v>
+        <v>65.24695242424302</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.03068052520568</v>
+        <v>14.79199265988669</v>
       </c>
       <c r="C4" t="n">
-        <v>63.35414285045516</v>
+        <v>152.7569975376909</v>
       </c>
       <c r="D4" t="n">
-        <v>88.35631163450869</v>
+        <v>64.54107582488956</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.56443248114646</v>
+        <v>13.67083678163684</v>
       </c>
       <c r="C5" t="n">
-        <v>96.33399347921829</v>
+        <v>163.9764103018235</v>
       </c>
       <c r="D5" t="n">
-        <v>65.89981464756715</v>
+        <v>41.82245220091413</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.7686360036298</v>
+        <v>9.418887474543901</v>
       </c>
       <c r="C6" t="n">
-        <v>110.4907953744573</v>
+        <v>93.34358997208251</v>
       </c>
       <c r="D6" t="n">
-        <v>47.69821221083129</v>
+        <v>29.38370878810704</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.7455727803466</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>114.2636518018778</v>
+        <v>48.20872101703962</v>
       </c>
       <c r="D7" t="n">
-        <v>39.82459562277186</v>
+        <v>29.10489244010094</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.52143120414207</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>84.19959185472769</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>47.03749600587317</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>37.29659528433633</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.682993771483339</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.15629947923549</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.682993771483339</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.001423716060751</v>
+        <v>1.201659189998096</v>
       </c>
       <c r="C2" t="n">
-        <v>10.27497147264712</v>
+        <v>14.42874600931537</v>
       </c>
       <c r="D2" t="n">
-        <v>32.2710287862969</v>
+        <v>26.87632515146068</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.36573422979433</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C3" t="n">
-        <v>21.74571164906685</v>
+        <v>30.29182541453534</v>
       </c>
       <c r="D3" t="n">
-        <v>87.46881170986957</v>
+        <v>66.56249434793374</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.55020498720149</v>
+        <v>15.43012866764712</v>
       </c>
       <c r="C4" t="n">
-        <v>55.08390018988003</v>
+        <v>135.2975963653657</v>
       </c>
       <c r="D4" t="n">
-        <v>105.4073057618673</v>
+        <v>80.73696770184918</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.96971435655115</v>
+        <v>17.9905266803228</v>
       </c>
       <c r="C5" t="n">
-        <v>106.3232763699296</v>
+        <v>225.3356418172492</v>
       </c>
       <c r="D5" t="n">
-        <v>80.87146713733101</v>
+        <v>53.97158004096841</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.12839763174064</v>
+        <v>13.52455637370406</v>
       </c>
       <c r="C6" t="n">
-        <v>129.7310868822863</v>
+        <v>177.5500540607399</v>
       </c>
       <c r="D6" t="n">
-        <v>56.31206656789281</v>
+        <v>34.97868895460962</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.4890178343687</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>136.7810171464826</v>
+        <v>90.36889442821465</v>
       </c>
       <c r="D7" t="n">
-        <v>43.59745205019235</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.94835258676919</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>115.6596970373167</v>
+        <v>45.98015372839936</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.31562403914873</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>74.32811868852599</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.864464138818037</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2549757872822</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.847522156170292</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.111379458936394</v>
+        <v>0.6567892141411161</v>
       </c>
       <c r="C2" t="n">
-        <v>9.63094497866121</v>
+        <v>6.299875018151782</v>
       </c>
       <c r="D2" t="n">
-        <v>41.25107503704248</v>
+        <v>18.29388672093506</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.76472470834603</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C3" t="n">
-        <v>30.17892442854695</v>
+        <v>44.57625451132643</v>
       </c>
       <c r="D3" t="n">
-        <v>91.18472677044375</v>
+        <v>72.99294181075035</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.09900195387546</v>
+        <v>16.61706164208151</v>
       </c>
       <c r="C4" t="n">
-        <v>54.05011985730815</v>
+        <v>126.133963293926</v>
       </c>
       <c r="D4" t="n">
-        <v>120.9395361907561</v>
+        <v>92.67011104696917</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.11697651218817</v>
+        <v>17.7450897542611</v>
       </c>
       <c r="C5" t="n">
-        <v>103.9179944945249</v>
+        <v>264.6300936797278</v>
       </c>
       <c r="D5" t="n">
-        <v>95.18043992672828</v>
+        <v>59.86206626644928</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.59633143376788</v>
+        <v>10.82769543013807</v>
       </c>
       <c r="C6" t="n">
-        <v>145.7109942643116</v>
+        <v>214.9840940236708</v>
       </c>
       <c r="D6" t="n">
-        <v>66.53598715991909</v>
+        <v>35.70321876034376</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.39405034896402</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>159.8373619807189</v>
+        <v>83.30227445304611</v>
       </c>
       <c r="D7" t="n">
-        <v>48.20872101703962</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.29182541453534</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>143.7818600254666</v>
+        <v>40.88979188187965</v>
       </c>
       <c r="D8" t="n">
-        <v>41.0566889916016</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.19687362466387</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>103.8374911827766</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>62.35079669671494</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.98167525545134</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.05883241345935</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.030834673315006</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.420122423917</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.03854334164376</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.652903281053134</v>
+        <v>0.7431830121148354</v>
       </c>
       <c r="C2" t="n">
-        <v>6.548257187326225</v>
+        <v>6.985134915716055</v>
       </c>
       <c r="D2" t="n">
-        <v>33.70045344368026</v>
+        <v>15.46841682811275</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.88668240785089</v>
+        <v>3.853359739168731</v>
       </c>
       <c r="C3" t="n">
-        <v>43.12817664756238</v>
+        <v>34.07155407588555</v>
       </c>
       <c r="D3" t="n">
-        <v>97.87533737488576</v>
+        <v>71.32887945205201</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.22891144600553</v>
+        <v>13.83478864824605</v>
       </c>
       <c r="C4" t="n">
-        <v>81.96218883674922</v>
+        <v>118.489093920956</v>
       </c>
       <c r="D4" t="n">
-        <v>114.3156844302029</v>
+        <v>105.7008483254371</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.49522711576368</v>
+        <v>21.05848825609409</v>
       </c>
       <c r="C5" t="n">
-        <v>87.05647767408593</v>
+        <v>251.2783249019712</v>
       </c>
       <c r="D5" t="n">
-        <v>65.33530971762524</v>
+        <v>76.20816554215867</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.17615911188346</v>
+        <v>16.06041069377357</v>
       </c>
       <c r="C6" t="n">
-        <v>105.2580801108218</v>
+        <v>313.8421608505076</v>
       </c>
       <c r="D6" t="n">
-        <v>31.71830482880595</v>
+        <v>44.55858305264999</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.06201433628357</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>101.0885976108856</v>
+        <v>182.2349541054057</v>
       </c>
       <c r="D7" t="n">
-        <v>28.86534600026472</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>76.52232480751763</v>
+        <v>69.59609475405638</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>47.59218345877262</v>
+        <v>36.16562192904399</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.98534020436108</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.59224021203486</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.27762328278614</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.538218726105504</v>
+        <v>0.3799363615435156</v>
       </c>
       <c r="C2" t="n">
-        <v>2.889283493598362</v>
+        <v>5.097234080449439</v>
       </c>
       <c r="D2" t="n">
-        <v>23.02787415081318</v>
+        <v>12.15305483087127</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.78850763742621</v>
+        <v>3.328124717396687</v>
       </c>
       <c r="C3" t="n">
-        <v>34.73423377625215</v>
+        <v>31.44537896702533</v>
       </c>
       <c r="D3" t="n">
-        <v>101.8415981000429</v>
+        <v>68.78615289805276</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.65230674844316</v>
+        <v>11.67788894201581</v>
       </c>
       <c r="C4" t="n">
-        <v>97.59652102687967</v>
+        <v>106.798442258785</v>
       </c>
       <c r="D4" t="n">
-        <v>134.5573585963636</v>
+        <v>114.2135826689612</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.17048960983623</v>
+        <v>22.16295442337175</v>
       </c>
       <c r="C5" t="n">
-        <v>118.5460352878024</v>
+        <v>246.934091310679</v>
       </c>
       <c r="D5" t="n">
-        <v>83.86579763528378</v>
+        <v>89.97717709422018</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.00635781677777</v>
+        <v>19.32079481957723</v>
       </c>
       <c r="C6" t="n">
-        <v>123.572583533546</v>
+        <v>358.1189823120388</v>
       </c>
       <c r="D6" t="n">
-        <v>39.48687441251096</v>
+        <v>51.84413276586557</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.98405535702057</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>125.1630148144258</v>
+        <v>267.1541670273463</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>37.84833749412304</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>97.88515485192822</v>
+        <v>107.4817386609408</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>54.0265579124062</v>
+        <v>44.15312125079604</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>39.67831521483909</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.816053326407352</v>
+        <v>0.2974695543867835</v>
       </c>
       <c r="C2" t="n">
-        <v>4.255876297909923</v>
+        <v>5.870851271395926</v>
       </c>
       <c r="D2" t="n">
-        <v>19.07143090269854</v>
+        <v>20.61277479836603</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.35591675275186</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C3" t="n">
-        <v>22.3445777486574</v>
+        <v>25.67761120457532</v>
       </c>
       <c r="D3" t="n">
-        <v>97.72316648072751</v>
+        <v>63.90686680794612</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.22961545626929</v>
+        <v>9.189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>91.99368687874312</v>
+        <v>94.53346818962962</v>
       </c>
       <c r="D4" t="n">
-        <v>151.7104544849638</v>
+        <v>118.9485518465436</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.71736413883072</v>
+        <v>20.61670178918302</v>
       </c>
       <c r="C5" t="n">
-        <v>148.5875150377548</v>
+        <v>224.6238747316703</v>
       </c>
       <c r="D5" t="n">
-        <v>108.1640533153924</v>
+        <v>105.9060335956247</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.43403996293088</v>
+        <v>23.38621206286328</v>
       </c>
       <c r="C6" t="n">
-        <v>155.5323982975967</v>
+        <v>373.4548632000783</v>
       </c>
       <c r="D6" t="n">
-        <v>53.05168244208915</v>
+        <v>64.00013283984957</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.36818075128833</v>
+        <v>12.69596131131975</v>
       </c>
       <c r="C7" t="n">
-        <v>150.3752776071882</v>
+        <v>368.5421976880271</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>42.4596064609703</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.51866588747858</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>130.263194137988</v>
+        <v>204.4489594093982</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>84.09061785955626</v>
+        <v>77.43436842476289</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>46.40721397974673</v>
+        <v>39.43189654107314</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>38.43836786437537</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.263910205993145</v>
+        <v>0.2091122610045706</v>
       </c>
       <c r="C2" t="n">
-        <v>1.997856578142259</v>
+        <v>3.334015203622168</v>
       </c>
       <c r="D2" t="n">
-        <v>13.1750541909922</v>
+        <v>15.17192902143021</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.40991287648544</v>
+        <v>3.264311116620645</v>
       </c>
       <c r="C3" t="n">
-        <v>21.25974653546468</v>
+        <v>28.74557278034661</v>
       </c>
       <c r="D3" t="n">
-        <v>95.11171758743099</v>
+        <v>71.01962892521426</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.75212621910685</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="C4" t="n">
-        <v>88.39459979497431</v>
+        <v>133.6767309056542</v>
       </c>
       <c r="D4" t="n">
-        <v>166.1961418611255</v>
+        <v>118.8847382457675</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.9508401659922</v>
+        <v>13.74446785945535</v>
       </c>
       <c r="C5" t="n">
-        <v>176.0764507566655</v>
+        <v>325.1548396465436</v>
       </c>
       <c r="D5" t="n">
-        <v>114.6681318560275</v>
+        <v>96.38308086443064</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.20132469929539</v>
+        <v>7.84907289545325</v>
       </c>
       <c r="C6" t="n">
-        <v>190.5110872522063</v>
+        <v>315.9352469559619</v>
       </c>
       <c r="D6" t="n">
-        <v>52.00513938936205</v>
+        <v>55.6680400739069</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.92310488389926</v>
+        <v>3.53330998758427</v>
       </c>
       <c r="C7" t="n">
-        <v>162.4723728189174</v>
+        <v>143.7877505116921</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>102.808619588726</v>
+        <v>57.07881152490955</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>35.38905949498476</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>23.77302065833652</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.357176237896592</v>
+        <v>0.129590696960579</v>
       </c>
       <c r="C2" t="n">
-        <v>6.970408700152354</v>
+        <v>1.818196748265093</v>
       </c>
       <c r="D2" t="n">
-        <v>13.15443748920301</v>
+        <v>10.57047753162541</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.10004045484194</v>
+        <v>2.056761440397068</v>
       </c>
       <c r="C3" t="n">
-        <v>14.27952035826986</v>
+        <v>20.64124548178919</v>
       </c>
       <c r="D3" t="n">
-        <v>84.73955309206343</v>
+        <v>66.6852128109646</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.12300586713388</v>
+        <v>9.942159000907449</v>
       </c>
       <c r="C4" t="n">
-        <v>71.49675830947821</v>
+        <v>100.0724887369901</v>
       </c>
       <c r="D4" t="n">
-        <v>174.3770454806142</v>
+        <v>120.5438918659446</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.73119072214818</v>
+        <v>13.30268139254428</v>
       </c>
       <c r="C5" t="n">
-        <v>171.3395180836746</v>
+        <v>258.9359569950963</v>
       </c>
       <c r="D5" t="n">
-        <v>143.7524075943392</v>
+        <v>102.8626157124596</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.57366912111219</v>
+        <v>7.607562960208536</v>
       </c>
       <c r="C6" t="n">
-        <v>232.0910477701715</v>
+        <v>330.6271013500154</v>
       </c>
       <c r="D6" t="n">
-        <v>69.59511300635215</v>
+        <v>58.04288777047993</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.32530264747096</v>
+        <v>2.694897448157494</v>
       </c>
       <c r="C7" t="n">
-        <v>214.1545172135822</v>
+        <v>191.7569250888955</v>
       </c>
       <c r="D7" t="n">
-        <v>40.24380189248525</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
-        <v>149.5398103108741</v>
+        <v>67.25953521794897</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7952820603647</v>
+        <v>26.11939767148639</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>69.11405663127118</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>16.37064296831556</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>12.79413608174443</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.05884810899257</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.458296251434013</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.614974973486003</v>
+        <v>0.1973312885536089</v>
       </c>
       <c r="C2" t="n">
-        <v>3.454770171244526</v>
+        <v>7.521169162234814</v>
       </c>
       <c r="D2" t="n">
-        <v>10.78548027885546</v>
+        <v>9.17541404389069</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.50470043544087</v>
+        <v>1.212458414744811</v>
       </c>
       <c r="C3" t="n">
-        <v>20.35653864755761</v>
+        <v>13.03760951239764</v>
       </c>
       <c r="D3" t="n">
-        <v>77.85259294677206</v>
+        <v>60.10259445398973</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.34524070119216</v>
+        <v>6.917394324123026</v>
       </c>
       <c r="C4" t="n">
-        <v>57.8789359038707</v>
+        <v>73.93443785912304</v>
       </c>
       <c r="D4" t="n">
-        <v>176.9168267915007</v>
+        <v>126.0063360923739</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.78090000216628</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="C5" t="n">
-        <v>161.9883712007237</v>
+        <v>222.8321851714198</v>
       </c>
       <c r="D5" t="n">
-        <v>164.197303535279</v>
+        <v>120.7795113149639</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.21519234034186</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>256.8860677886289</v>
+        <v>371.4825320622464</v>
       </c>
       <c r="D6" t="n">
-        <v>84.44797402390215</v>
+        <v>74.22405343187586</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.12757044828985</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>260.8660729816455</v>
+        <v>331.7718191731671</v>
       </c>
       <c r="D7" t="n">
-        <v>45.8132566186774</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>188.0095941017854</v>
+        <v>154.046032273367</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>79.87499321752047</v>
+        <v>52.69530802544753</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>22.18749811597791</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>23.63066724122073</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.35653864755762</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.237803928605981</v>
+        <v>0.3279037332184347</v>
       </c>
       <c r="C2" t="n">
-        <v>16.94791061841268</v>
+        <v>15.87289688226243</v>
       </c>
       <c r="D2" t="n">
-        <v>16.89391449467911</v>
+        <v>10.58225850407637</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.114144775599888</v>
+        <v>0.9424777960769379</v>
       </c>
       <c r="C3" t="n">
-        <v>16.96460032938488</v>
+        <v>21.12230185687012</v>
       </c>
       <c r="D3" t="n">
-        <v>69.99861131279758</v>
+        <v>54.1286596736479</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.99766095615978</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C4" t="n">
-        <v>54.53510322320607</v>
+        <v>53.55237377125501</v>
       </c>
       <c r="D4" t="n">
-        <v>175.2066222907028</v>
+        <v>127.1039300257218</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.3573658310084</v>
+        <v>12.76272015520854</v>
       </c>
       <c r="C5" t="n">
-        <v>137.6901155206152</v>
+        <v>181.7951311339031</v>
       </c>
       <c r="D5" t="n">
-        <v>181.2797135891736</v>
+        <v>135.7757074973339</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.58753676215866</v>
+        <v>15.45663585566179</v>
       </c>
       <c r="C6" t="n">
-        <v>258.0936174648525</v>
+        <v>361.7416313407095</v>
       </c>
       <c r="D6" t="n">
-        <v>108.1561993337584</v>
+        <v>90.32471578152357</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.48228446915921</v>
+        <v>9.222537933694536</v>
       </c>
       <c r="C7" t="n">
-        <v>309.6736600982757</v>
+        <v>426.8717557881471</v>
       </c>
       <c r="D7" t="n">
-        <v>55.51488743204438</v>
+        <v>49.40645321622073</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>3.421390749300134</v>
       </c>
       <c r="C8" t="n">
-        <v>249.8449732537707</v>
+        <v>280.8043871071939</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>137.2296758473234</v>
+        <v>112.2687404668482</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>23.62968549351647</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>54.52135875534661</v>
+        <v>40.00131020953629</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.824709129296326</v>
+        <v>3.239767424014474</v>
       </c>
       <c r="C2" t="n">
-        <v>9.101782966072179</v>
+        <v>12.44168865591983</v>
       </c>
       <c r="D2" t="n">
-        <v>13.97223332684061</v>
+        <v>7.721445693901163</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.314961086613979</v>
+        <v>0.3092505268377453</v>
       </c>
       <c r="C2" t="n">
-        <v>9.627017987844223</v>
+        <v>13.26046624126167</v>
       </c>
       <c r="D2" t="n">
-        <v>12.43383467428585</v>
+        <v>20.45962215650353</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.48644813968768</v>
+        <v>0.9817477042468105</v>
       </c>
       <c r="C3" t="n">
-        <v>34.1500938922253</v>
+        <v>38.85757413408876</v>
       </c>
       <c r="D3" t="n">
-        <v>77.13100838415066</v>
+        <v>50.51582812201963</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.94807484932871</v>
+        <v>3.331069960509427</v>
       </c>
       <c r="C4" t="n">
-        <v>79.00123776074084</v>
+        <v>52.48030527821749</v>
       </c>
       <c r="D4" t="n">
-        <v>178.1420479264007</v>
+        <v>125.2022847225957</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.66765485881262</v>
+        <v>10.55378782065321</v>
       </c>
       <c r="C5" t="n">
-        <v>213.2601450550134</v>
+        <v>146.2313205475624</v>
       </c>
       <c r="D5" t="n">
-        <v>164.5654589243716</v>
+        <v>144.9305048394354</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.91827826083604</v>
+        <v>16.06041069377357</v>
       </c>
       <c r="C6" t="n">
-        <v>254.55147174793</v>
+        <v>330.7076046617636</v>
       </c>
       <c r="D6" t="n">
-        <v>84.7699872708951</v>
+        <v>106.9083980016607</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>12.6360747013607</v>
       </c>
       <c r="C7" t="n">
-        <v>175.7073136198686</v>
+        <v>465.0195263320654</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>59.22785724950582</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>101.1396484915064</v>
+        <v>397.5489153577034</v>
       </c>
       <c r="D8" t="n">
-        <v>24.95111790343269</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60155896745857</v>
+        <v>203.1265452517777</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>25.29374785221481</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>22.49183990429443</v>
+        <v>75.58966448848317</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.34806277111788</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.34962535589888</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.384305320717008</v>
+        <v>3.901465376676824</v>
       </c>
       <c r="C2" t="n">
-        <v>6.780931393232719</v>
+        <v>10.84438514111027</v>
       </c>
       <c r="D2" t="n">
-        <v>18.91435127001905</v>
+        <v>14.42285552308989</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.37492981203104</v>
+        <v>5.360342465187586</v>
       </c>
       <c r="C3" t="n">
-        <v>22.93362637120549</v>
+        <v>24.5633275602552</v>
       </c>
       <c r="D3" t="n">
-        <v>14.87347771933918</v>
+        <v>8.315403054970485</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39704200765981</v>
+        <v>11.67804077024728</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13745521657195</v>
+        <v>59.94727595393605</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576122589136448</v>
+        <v>0.7785360513498188</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.819399480147592</v>
+        <v>2.460259746842507</v>
       </c>
       <c r="C2" t="n">
-        <v>3.784637399871454</v>
+        <v>7.142214548395546</v>
       </c>
       <c r="D2" t="n">
-        <v>17.50750680983337</v>
+        <v>14.68203691701105</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.18687622117216</v>
+        <v>10.52433538952581</v>
       </c>
       <c r="C3" t="n">
-        <v>25.12783249019711</v>
+        <v>36.44738352016284</v>
       </c>
       <c r="D3" t="n">
-        <v>27.16495897650924</v>
+        <v>18.91827826083604</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.40911105523044</v>
+        <v>6.777004402415732</v>
       </c>
       <c r="C4" t="n">
-        <v>35.49312475163494</v>
+        <v>40.45782289201105</v>
       </c>
       <c r="D4" t="n">
-        <v>22.8707945181337</v>
+        <v>18.55699510567321</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.58292145661112</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43752024135479</v>
+        <v>13.62874867493534</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12511292545307</v>
+        <v>73.75558106435598</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250004261337852</v>
+        <v>1.603382197051217</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.396266219617217</v>
+        <v>2.170644174089698</v>
       </c>
       <c r="C2" t="n">
-        <v>5.786420968830701</v>
+        <v>12.05389831274234</v>
       </c>
       <c r="D2" t="n">
-        <v>16.13796876240907</v>
+        <v>18.69443978426776</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.34748193404114</v>
+        <v>9.419869222248145</v>
       </c>
       <c r="C3" t="n">
-        <v>18.82010349041136</v>
+        <v>31.00850123863551</v>
       </c>
       <c r="D3" t="n">
-        <v>34.86676971632547</v>
+        <v>26.67899386290707</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.24015263910875</v>
+        <v>15.00895890252524</v>
       </c>
       <c r="C4" t="n">
-        <v>51.65072846812894</v>
+        <v>71.93069079475531</v>
       </c>
       <c r="D4" t="n">
-        <v>31.33247798103695</v>
+        <v>24.15982925380975</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.61545799957152</v>
+        <v>6.724971774090653</v>
       </c>
       <c r="C5" t="n">
-        <v>39.71169463678348</v>
+        <v>46.82936549257286</v>
       </c>
       <c r="D5" t="n">
-        <v>30.87596529856219</v>
+        <v>26.60536278508857</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.427682146153116</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.01453059358123</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72818586606672</v>
+        <v>14.83823139923892</v>
       </c>
       <c r="C21" t="n">
-        <v>102.041933783007</v>
+        <v>87.38069601774029</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182046466516679</v>
+        <v>2.473038566539819</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.569053815564656</v>
+        <v>2.452405765208532</v>
       </c>
       <c r="C2" t="n">
-        <v>5.098215828153687</v>
+        <v>14.0978970329842</v>
       </c>
       <c r="D2" t="n">
-        <v>17.64396974072368</v>
+        <v>21.39620946635499</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.24301576676348</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C3" t="n">
-        <v>20.90631736193583</v>
+        <v>40.64926369433918</v>
       </c>
       <c r="D3" t="n">
-        <v>39.37299167881833</v>
+        <v>35.44109212330985</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.96686692442964</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C4" t="n">
-        <v>49.11094715724244</v>
+        <v>75.35109979635119</v>
       </c>
       <c r="D4" t="n">
-        <v>41.19806066101315</v>
+        <v>32.09824119034946</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.86905200690346</v>
+        <v>14.89802141194535</v>
       </c>
       <c r="C5" t="n">
-        <v>69.4095626902495</v>
+        <v>95.91675070491338</v>
       </c>
       <c r="D5" t="n">
-        <v>34.70478134512475</v>
+        <v>29.15790681613028</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.59247689174634</v>
+        <v>6.963536466222627</v>
       </c>
       <c r="C6" t="n">
-        <v>39.00385454202154</v>
+        <v>45.36361617013237</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>33.61013265488955</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.40156017323271</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.13486895504285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0513798257107</v>
+        <v>16.07713660234975</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7637636248745</v>
+        <v>100.6936450357695</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017126608570232</v>
+        <v>3.384660337336791</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.194427103169874</v>
+        <v>1.721003725544659</v>
       </c>
       <c r="C2" t="n">
-        <v>8.532369297609028</v>
+        <v>8.811185645615122</v>
       </c>
       <c r="D2" t="n">
-        <v>31.39727332951724</v>
+        <v>24.53780211994478</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.15680189523901</v>
+        <v>8.349764224619122</v>
       </c>
       <c r="C3" t="n">
-        <v>19.04590546238812</v>
+        <v>48.57196766761095</v>
       </c>
       <c r="D3" t="n">
-        <v>41.41993564217293</v>
+        <v>43.81540004053515</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.27094667083889</v>
+        <v>16.46390900021901</v>
       </c>
       <c r="C4" t="n">
-        <v>42.58919715793088</v>
+        <v>89.07102396320037</v>
       </c>
       <c r="D4" t="n">
-        <v>44.55465606183299</v>
+        <v>42.06592563156733</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.89297380470387</v>
+        <v>20.37126486312132</v>
       </c>
       <c r="C5" t="n">
-        <v>59.5920856477814</v>
+        <v>119.3068897585937</v>
       </c>
       <c r="D5" t="n">
-        <v>33.20761609614836</v>
+        <v>33.60031517784709</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.67927160034756</v>
+        <v>13.48430471782994</v>
       </c>
       <c r="C6" t="n">
-        <v>51.6831261423691</v>
+        <v>100.7498946529204</v>
       </c>
       <c r="D6" t="n">
-        <v>31.63780151705772</v>
+        <v>35.58246379272141</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>24.852943133008</v>
+        <v>42.04040019125691</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.054768158415524</v>
+        <v>17.33715335313352</v>
       </c>
       <c r="C21" t="n">
-        <v>66.13845148514552</v>
+        <v>114.4252121306812</v>
       </c>
       <c r="D21" t="n">
-        <v>4.409230099009702</v>
+        <v>4.334288338283379</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.454189334167778</v>
+        <v>1.698423528346982</v>
       </c>
       <c r="C2" t="n">
-        <v>6.408849013323178</v>
+        <v>12.73817646260236</v>
       </c>
       <c r="D2" t="n">
-        <v>32.68434456978481</v>
+        <v>35.27026802277091</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.67989349515331</v>
+        <v>7.01458734684346</v>
       </c>
       <c r="C3" t="n">
-        <v>28.26451640526567</v>
+        <v>40.82106954258238</v>
       </c>
       <c r="D3" t="n">
-        <v>57.78566987196726</v>
+        <v>51.59575059669112</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.90832191507333</v>
+        <v>16.22141731727005</v>
       </c>
       <c r="C4" t="n">
-        <v>45.88197895797468</v>
+        <v>104.5777289517787</v>
       </c>
       <c r="D4" t="n">
-        <v>55.49230723484671</v>
+        <v>52.09742367356125</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.71612034921921</v>
+        <v>22.33476027161494</v>
       </c>
       <c r="C5" t="n">
-        <v>70.83309686140738</v>
+        <v>141.7643684932394</v>
       </c>
       <c r="D5" t="n">
-        <v>42.7551125199486</v>
+        <v>40.2761995667254</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.66168225712913</v>
+        <v>20.04532462531138</v>
       </c>
       <c r="C6" t="n">
-        <v>77.56494086942776</v>
+        <v>143.4569015353609</v>
       </c>
       <c r="D6" t="n">
-        <v>35.54221213684728</v>
+        <v>37.71580155404972</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.13890945238431</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="C7" t="n">
-        <v>54.37704184282233</v>
+        <v>90.18923459833748</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>27.28767743954009</v>
+        <v>39.8884092235479</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.34594471145593</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>32.26022956155019</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.2771359268414</v>
+        <v>17.72422757367649</v>
       </c>
       <c r="C21" t="n">
-        <v>75.50028524097954</v>
+        <v>127.6144385304707</v>
       </c>
       <c r="D21" t="n">
-        <v>5.457851945131051</v>
+        <v>5.317268272102948</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.729659528433633</v>
+        <v>1.609084487260522</v>
       </c>
       <c r="C2" t="n">
-        <v>3.615776794741003</v>
+        <v>8.050331174823844</v>
       </c>
       <c r="D2" t="n">
-        <v>35.53632165062179</v>
+        <v>27.9483936444982</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.97794388661684</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="C3" t="n">
-        <v>26.24702487303848</v>
+        <v>64.17193868809277</v>
       </c>
       <c r="D3" t="n">
-        <v>70.52384633456963</v>
+        <v>56.6370250579985</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.57122259961817</v>
+        <v>10.72068493037517</v>
       </c>
       <c r="C4" t="n">
-        <v>60.5591071364645</v>
+        <v>134.0085616296896</v>
       </c>
       <c r="D4" t="n">
-        <v>71.99450439553134</v>
+        <v>49.07265899677682</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.68023765251858</v>
+        <v>11.29009859883832</v>
       </c>
       <c r="C5" t="n">
-        <v>78.85888434362505</v>
+        <v>85.70657458074656</v>
       </c>
       <c r="D5" t="n">
-        <v>52.69530802544756</v>
+        <v>34.11573272257667</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.51704654943536</v>
+        <v>7.003788122096746</v>
       </c>
       <c r="C6" t="n">
-        <v>96.2819608508932</v>
+        <v>59.37119241432587</v>
       </c>
       <c r="D6" t="n">
-        <v>41.33845058272045</v>
+        <v>25.80131141531043</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.8823545064064</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>86.59603800079415</v>
+        <v>28.02693346083794</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>26.70942804173872</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>51.90500112352886</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>25.62656032395449</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.487033446469869</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.22912627278603</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.551154265661136</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
